--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486508_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486508_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.2981</v>
+        <v>6.2539</v>
       </c>
       <c r="E2" t="n">
-        <v>3.6496</v>
+        <v>3.3143</v>
       </c>
       <c r="F2" t="n">
-        <v>3.6486</v>
+        <v>2.9396</v>
       </c>
       <c r="G2" t="n">
         <v>4.2067</v>
@@ -610,13 +610,13 @@
         <v>2.3926</v>
       </c>
       <c r="S2" t="n">
-        <v>1.2638</v>
+        <v>0.2196</v>
       </c>
       <c r="T2" t="n">
-        <v>0.5312</v>
+        <v>0.1959</v>
       </c>
       <c r="U2" t="n">
-        <v>0.7327</v>
+        <v>0.0237</v>
       </c>
       <c r="V2" t="n">
         <v>-0.5649999999999999</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.5508</v>
+        <v>6.1713</v>
       </c>
       <c r="E3" t="n">
-        <v>3.0604</v>
+        <v>3.6192</v>
       </c>
       <c r="F3" t="n">
-        <v>2.4904</v>
+        <v>2.552</v>
       </c>
       <c r="G3" t="n">
         <v>5.7703</v>
@@ -688,13 +688,13 @@
         <v>1.9576</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.6545</v>
+        <v>-1.0341</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.2329</v>
+        <v>-0.6741</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.4216</v>
+        <v>-0.3599</v>
       </c>
       <c r="V3" t="n">
         <v>0.5649999999999999</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.8692</v>
+        <v>4.4626</v>
       </c>
       <c r="E4" t="n">
-        <v>1.2324</v>
+        <v>1.4559</v>
       </c>
       <c r="F4" t="n">
-        <v>2.6368</v>
+        <v>3.0067</v>
       </c>
       <c r="G4" t="n">
         <v>3.6867</v>
@@ -766,13 +766,13 @@
         <v>1.5225</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.0344</v>
+        <v>-0.441</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.7534999999999999</v>
+        <v>-0.5299</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.281</v>
+        <v>0.08890000000000001</v>
       </c>
       <c r="V4" t="n">
         <v>1.8695</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.2266</v>
+        <v>3.5541</v>
       </c>
       <c r="E5" t="n">
-        <v>0.827</v>
+        <v>0.9387</v>
       </c>
       <c r="F5" t="n">
-        <v>2.3997</v>
+        <v>2.6154</v>
       </c>
       <c r="G5" t="n">
         <v>3.5058</v>
@@ -844,13 +844,13 @@
         <v>1.9576</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.1492</v>
+        <v>-0.8217</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.4879</v>
+        <v>-0.3761</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.6613</v>
+        <v>-0.4455</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.0983</v>
+        <v>1.6167</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.3323</v>
+        <v>-0.444</v>
       </c>
       <c r="F6" t="n">
-        <v>2.4305</v>
+        <v>2.0607</v>
       </c>
       <c r="G6" t="n">
         <v>1.691</v>
@@ -922,13 +922,13 @@
         <v>0.6525</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2773</v>
+        <v>-0.2043</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.2139</v>
+        <v>-0.3256</v>
       </c>
       <c r="U6" t="n">
-        <v>0.4912</v>
+        <v>0.1214</v>
       </c>
       <c r="V6" t="n">
         <v>0.5649999999999999</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.7843</v>
+        <v>1.0271</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.5</v>
+        <v>-2.1647</v>
       </c>
       <c r="F7" t="n">
-        <v>3.2843</v>
+        <v>3.1918</v>
       </c>
       <c r="G7" t="n">
         <v>0.7672</v>
@@ -1000,13 +1000,13 @@
         <v>1.5225</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.2227</v>
+        <v>0.0201</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.8904</v>
+        <v>-0.5552</v>
       </c>
       <c r="U7" t="n">
-        <v>0.6677999999999999</v>
+        <v>0.5753</v>
       </c>
       <c r="V7" t="n">
         <v>-0.1952</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>P. CORDOBA MURO</t>
+          <t>J. GARCIA SANCHEZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6531</v>
+        <v>0.5264</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.478</v>
+        <v>-3.3511</v>
       </c>
       <c r="F8" t="n">
-        <v>2.1311</v>
+        <v>3.8775</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.0117</v>
+        <v>0.2069</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.8547</v>
+        <v>-0.9582000000000001</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.157</v>
+        <v>1.165</v>
       </c>
       <c r="J8" t="n">
-        <v>-2.0674</v>
+        <v>-1.5269</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.6538</v>
+        <v>-0.6903</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.4136</v>
+        <v>-0.8366</v>
       </c>
       <c r="M8" t="n">
-        <v>1.0557</v>
+        <v>1.7338</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.2009</v>
+        <v>-0.2679</v>
       </c>
       <c r="O8" t="n">
-        <v>1.2566</v>
+        <v>2.0017</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>-0.435</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.0875</v>
+        <v>-2.1751</v>
       </c>
       <c r="R8" t="n">
-        <v>1.0875</v>
+        <v>1.7401</v>
       </c>
       <c r="S8" t="n">
-        <v>1.4696</v>
+        <v>0.015</v>
       </c>
       <c r="T8" t="n">
-        <v>1.4817</v>
+        <v>0.3509</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.0121</v>
+        <v>-0.3359</v>
       </c>
       <c r="V8" t="n">
-        <v>0.1952</v>
+        <v>0.7395</v>
       </c>
       <c r="W8" t="n">
-        <v>0.1952</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>0.7395</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. GARCIA SANCHEZ</t>
+          <t>S. CECCARDI</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.5765</v>
+        <v>0.3692</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.2393</v>
+        <v>1.2472</v>
       </c>
       <c r="F9" t="n">
-        <v>3.8159</v>
+        <v>-0.878</v>
       </c>
       <c r="G9" t="n">
-        <v>0.2069</v>
+        <v>1.5274</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.9582000000000001</v>
+        <v>-1.6696</v>
       </c>
       <c r="I9" t="n">
-        <v>1.165</v>
+        <v>3.197</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.5269</v>
+        <v>1.4671</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.6903</v>
+        <v>0.3562</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.8366</v>
+        <v>1.1108</v>
       </c>
       <c r="M9" t="n">
-        <v>1.7338</v>
+        <v>0.0603</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.2679</v>
+        <v>-2.0258</v>
       </c>
       <c r="O9" t="n">
-        <v>2.0017</v>
+        <v>2.0862</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.435</v>
+        <v>0.87</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.1751</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.7401</v>
+        <v>0.87</v>
       </c>
       <c r="S9" t="n">
-        <v>0.06510000000000001</v>
+        <v>-0.8983</v>
       </c>
       <c r="T9" t="n">
-        <v>0.4627</v>
+        <v>-0.2199</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.3975</v>
+        <v>-0.6784</v>
       </c>
       <c r="V9" t="n">
-        <v>0.7395</v>
+        <v>-1.13</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0.7395</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.0242</v>
+        <v>-0.1475</v>
       </c>
       <c r="E10" t="n">
         <v>-0.06850000000000001</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0443</v>
+        <v>-0.079</v>
       </c>
       <c r="G10" t="n">
         <v>-0.216</v>
@@ -1234,13 +1234,13 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>0.1918</v>
+        <v>0.06850000000000001</v>
       </c>
       <c r="T10" t="n">
         <v>-0.06850000000000001</v>
       </c>
       <c r="U10" t="n">
-        <v>0.2603</v>
+        <v>0.137</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>N. MC MULLEN</t>
+          <t>P. CORDOBA MURO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.2604</v>
+        <v>-0.4953</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.6669</v>
+        <v>-2.5956</v>
       </c>
       <c r="F11" t="n">
-        <v>0.4065</v>
+        <v>2.1003</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.233</v>
+        <v>-1.0117</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.4171</v>
+        <v>-0.8547</v>
       </c>
       <c r="I11" t="n">
-        <v>1.1841</v>
+        <v>-0.157</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.9907</v>
+        <v>-2.0674</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.0672</v>
+        <v>-0.6538</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0765</v>
+        <v>-1.4136</v>
       </c>
       <c r="M11" t="n">
-        <v>0.7577</v>
+        <v>1.0557</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.3499</v>
+        <v>-0.2009</v>
       </c>
       <c r="O11" t="n">
-        <v>1.1076</v>
+        <v>1.2566</v>
       </c>
       <c r="P11" t="n">
-        <v>0.435</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-1.0875</v>
       </c>
       <c r="R11" t="n">
-        <v>0.435</v>
+        <v>1.0875</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.4624</v>
+        <v>0.3212</v>
       </c>
       <c r="T11" t="n">
-        <v>0.1286</v>
+        <v>0.3641</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.591</v>
+        <v>-0.043</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>0.1952</v>
       </c>
       <c r="W11" t="n">
         <v>0.1952</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.1952</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>S. CECCARDI</t>
+          <t>N. MC MULLEN</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.6096</v>
+        <v>-0.534</v>
       </c>
       <c r="E12" t="n">
-        <v>0.5766</v>
+        <v>-1.0022</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.1862</v>
+        <v>0.4681</v>
       </c>
       <c r="G12" t="n">
-        <v>1.5274</v>
+        <v>-0.233</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.6696</v>
+        <v>-1.4171</v>
       </c>
       <c r="I12" t="n">
-        <v>3.197</v>
+        <v>1.1841</v>
       </c>
       <c r="J12" t="n">
-        <v>1.4671</v>
+        <v>-0.9907</v>
       </c>
       <c r="K12" t="n">
-        <v>0.3562</v>
+        <v>-1.0672</v>
       </c>
       <c r="L12" t="n">
-        <v>1.1108</v>
+        <v>0.0765</v>
       </c>
       <c r="M12" t="n">
-        <v>0.0603</v>
+        <v>0.7577</v>
       </c>
       <c r="N12" t="n">
-        <v>-2.0258</v>
+        <v>-0.3499</v>
       </c>
       <c r="O12" t="n">
-        <v>2.0862</v>
+        <v>1.1076</v>
       </c>
       <c r="P12" t="n">
-        <v>0.87</v>
+        <v>0.435</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>0.87</v>
+        <v>0.435</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.877</v>
+        <v>-0.736</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.8904</v>
+        <v>-0.2067</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.9866</v>
+        <v>-0.5294</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.13</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>0.1952</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.13</v>
+        <v>-0.1952</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.7162</v>
+        <v>-2.3579</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.9703</v>
+        <v>-2.8586</v>
       </c>
       <c r="F13" t="n">
-        <v>0.2541</v>
+        <v>0.5007</v>
       </c>
       <c r="G13" t="n">
         <v>-2.1836</v>
@@ -1468,13 +1468,13 @@
         <v>1.0875</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.5326</v>
+        <v>-0.1742</v>
       </c>
       <c r="T13" t="n">
-        <v>0.1971</v>
+        <v>0.3088</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.7297</v>
+        <v>-0.4831</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>20.4465</v>
+        <v>20.4466</v>
       </c>
       <c r="E14" t="n">
-        <v>-1.909299999999999</v>
+        <v>-1.9094</v>
       </c>
       <c r="F14" t="n">
-        <v>22.356</v>
+        <v>22.3558</v>
       </c>
       <c r="G14" t="n">
         <v>17.7177</v>
@@ -1519,10 +1519,10 @@
         <v>24.4396</v>
       </c>
       <c r="J14" t="n">
-        <v>6.9221</v>
+        <v>6.922099999999999</v>
       </c>
       <c r="K14" t="n">
-        <v>0.6863</v>
+        <v>0.6862999999999998</v>
       </c>
       <c r="L14" t="n">
         <v>6.2357</v>
@@ -1549,10 +1549,10 @@
         <v>-3.6652</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.7362</v>
+        <v>-1.736300000000001</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.9288</v>
+        <v>-1.9289</v>
       </c>
       <c r="V14" t="n">
         <v>2.044</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>6.3214</v>
+        <v>4.0479</v>
       </c>
       <c r="E15" t="n">
-        <v>6.7183</v>
+        <v>5.1537</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.3969</v>
+        <v>-1.1059</v>
       </c>
       <c r="G15" t="n">
         <v>2.1972</v>
@@ -1624,13 +1624,13 @@
         <v>0.6525</v>
       </c>
       <c r="S15" t="n">
-        <v>3.8415</v>
+        <v>1.5679</v>
       </c>
       <c r="T15" t="n">
-        <v>2.1703</v>
+        <v>0.6057</v>
       </c>
       <c r="U15" t="n">
-        <v>1.6712</v>
+        <v>0.9622000000000001</v>
       </c>
       <c r="V15" t="n">
         <v>-0.3698</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>4.4306</v>
+        <v>3.8795</v>
       </c>
       <c r="E16" t="n">
-        <v>4.9347</v>
+        <v>4.5994</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.5041</v>
+        <v>-0.7199</v>
       </c>
       <c r="G16" t="n">
         <v>1.7234</v>
@@ -1702,13 +1702,13 @@
         <v>0.87</v>
       </c>
       <c r="S16" t="n">
-        <v>1.2297</v>
+        <v>0.6787</v>
       </c>
       <c r="T16" t="n">
-        <v>0.7487</v>
+        <v>0.4134</v>
       </c>
       <c r="U16" t="n">
-        <v>0.481</v>
+        <v>0.2653</v>
       </c>
       <c r="V16" t="n">
         <v>1.695</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.3536</v>
+        <v>-1.7159</v>
       </c>
       <c r="E17" t="n">
-        <v>-4.6868</v>
+        <v>-5.3574</v>
       </c>
       <c r="F17" t="n">
-        <v>3.3333</v>
+        <v>3.6415</v>
       </c>
       <c r="G17" t="n">
         <v>0.5679999999999999</v>
@@ -1780,13 +1780,13 @@
         <v>1.5225</v>
       </c>
       <c r="S17" t="n">
-        <v>0.9061</v>
+        <v>0.5438</v>
       </c>
       <c r="T17" t="n">
-        <v>0.7607</v>
+        <v>0.0901</v>
       </c>
       <c r="U17" t="n">
-        <v>0.1454</v>
+        <v>0.4536</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>T. MCGHIE</t>
+          <t>M. MOTOS CABODEVILLA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,64 +1813,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.3382</v>
+        <v>-2.088</v>
       </c>
       <c r="E18" t="n">
-        <v>-4.4397</v>
+        <v>-4.263</v>
       </c>
       <c r="F18" t="n">
-        <v>2.1015</v>
+        <v>2.175</v>
       </c>
       <c r="G18" t="n">
-        <v>-3.7425</v>
+        <v>-2.6183</v>
       </c>
       <c r="H18" t="n">
-        <v>0.3406</v>
+        <v>-0.8485</v>
       </c>
       <c r="I18" t="n">
-        <v>-4.0831</v>
+        <v>-1.7698</v>
       </c>
       <c r="J18" t="n">
-        <v>-3.4484</v>
+        <v>-3.7386</v>
       </c>
       <c r="K18" t="n">
-        <v>0.2769</v>
+        <v>-0.7966</v>
       </c>
       <c r="L18" t="n">
-        <v>-3.7253</v>
+        <v>-2.942</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.2942</v>
+        <v>1.1203</v>
       </c>
       <c r="N18" t="n">
-        <v>0.0636</v>
+        <v>-0.0519</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.3578</v>
+        <v>1.1722</v>
       </c>
       <c r="P18" t="n">
-        <v>0.435</v>
+        <v>1.0875</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.0875</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.5225</v>
+        <v>1.0875</v>
       </c>
       <c r="S18" t="n">
-        <v>0.9693000000000001</v>
+        <v>0.1824</v>
       </c>
       <c r="T18" t="n">
-        <v>0.0961</v>
+        <v>0.2151</v>
       </c>
       <c r="U18" t="n">
-        <v>0.8731</v>
+        <v>-0.0328</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>-0.7395</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>-0.7395</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M. MOTOS CABODEVILLA</t>
+          <t>J. NICOLAU ALEDON</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.5427</v>
+        <v>-2.4918</v>
       </c>
       <c r="E19" t="n">
-        <v>-4.9336</v>
+        <v>-2.3945</v>
       </c>
       <c r="F19" t="n">
-        <v>2.3908</v>
+        <v>-0.09719999999999999</v>
       </c>
       <c r="G19" t="n">
-        <v>-2.6183</v>
+        <v>-0.8374</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.8485</v>
+        <v>-0.584</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.7698</v>
+        <v>-0.2534</v>
       </c>
       <c r="J19" t="n">
-        <v>-3.7386</v>
+        <v>-0.4166</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.7966</v>
+        <v>-0.4166</v>
       </c>
       <c r="L19" t="n">
-        <v>-2.942</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>1.1203</v>
+        <v>-0.4208</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.0519</v>
+        <v>-0.1674</v>
       </c>
       <c r="O19" t="n">
-        <v>1.1722</v>
+        <v>-0.2534</v>
       </c>
       <c r="P19" t="n">
-        <v>1.0875</v>
+        <v>-1.305</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-2.1751</v>
       </c>
       <c r="R19" t="n">
-        <v>1.0875</v>
+        <v>0.87</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.2724</v>
+        <v>-0.1541</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.4554</v>
+        <v>0.1971</v>
       </c>
       <c r="U19" t="n">
-        <v>0.183</v>
+        <v>-0.3512</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.7395</v>
+        <v>-0.1952</v>
       </c>
       <c r="W19" t="n">
-        <v>-0.7395</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-0.1952</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. NICOLAU ALEDON</t>
+          <t>T. MCGHIE</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.9696</v>
+        <v>-2.5462</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.8416</v>
+        <v>-4.2162</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.128</v>
+        <v>1.67</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.8374</v>
+        <v>-3.7425</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.584</v>
+        <v>0.3406</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.2534</v>
+        <v>-4.0831</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.4166</v>
+        <v>-3.4484</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.4166</v>
+        <v>0.2769</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>-3.7253</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.4208</v>
+        <v>-0.2942</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.1674</v>
+        <v>0.0636</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.2534</v>
+        <v>-0.3578</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.305</v>
+        <v>0.435</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.1751</v>
+        <v>-1.0875</v>
       </c>
       <c r="R20" t="n">
-        <v>0.87</v>
+        <v>1.5225</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.632</v>
+        <v>0.7613</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.2499</v>
+        <v>0.3197</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.382</v>
+        <v>0.4416</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.1952</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.1952</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.242</v>
+        <v>-3.7604</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.0269</v>
+        <v>-1.9151</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.2151</v>
+        <v>-1.8453</v>
       </c>
       <c r="G21" t="n">
         <v>-3.8227</v>
@@ -2092,13 +2092,13 @@
         <v>0.6525</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.5069</v>
+        <v>-0.0252</v>
       </c>
       <c r="T21" t="n">
-        <v>0.1406</v>
+        <v>0.2524</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.6475</v>
+        <v>-0.2776</v>
       </c>
       <c r="V21" t="n">
         <v>-0.5649999999999999</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.544</v>
+        <v>-4.4515</v>
       </c>
       <c r="E22" t="n">
         <v>-4.5328</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.0112</v>
+        <v>0.0813</v>
       </c>
       <c r="G22" t="n">
         <v>-4.0919</v>
@@ -2170,13 +2170,13 @@
         <v>0.6525</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.2123</v>
+        <v>-0.1199</v>
       </c>
       <c r="T22" t="n">
         <v>0.4266</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.6389</v>
+        <v>-0.5465</v>
       </c>
       <c r="V22" t="n">
         <v>0.1952</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.9619</v>
+        <v>-4.9022</v>
       </c>
       <c r="E23" t="n">
-        <v>-6.2656</v>
+        <v>-5.4833</v>
       </c>
       <c r="F23" t="n">
-        <v>0.3038</v>
+        <v>0.5812</v>
       </c>
       <c r="G23" t="n">
         <v>-4.763</v>
@@ -2248,13 +2248,13 @@
         <v>1.305</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.5241</v>
+        <v>0.5357</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.9469</v>
+        <v>-0.1646</v>
       </c>
       <c r="U23" t="n">
-        <v>0.4229</v>
+        <v>0.7003</v>
       </c>
       <c r="V23" t="n">
         <v>0.1952</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-7.2465</v>
+        <v>-6.4181</v>
       </c>
       <c r="E24" t="n">
-        <v>-4.282</v>
+        <v>-3.9467</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.9645</v>
+        <v>-2.4713</v>
       </c>
       <c r="G24" t="n">
         <v>-2.3303</v>
@@ -2326,13 +2326,13 @@
         <v>1.7401</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.1337</v>
+        <v>-0.3052</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.7619</v>
+        <v>-0.4266</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.3718</v>
+        <v>0.1214</v>
       </c>
       <c r="V24" t="n">
         <v>-2.2599</v>
@@ -2359,19 +2359,19 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-20.4465</v>
+        <v>-20.4467</v>
       </c>
       <c r="E25" t="n">
-        <v>-22.356</v>
+        <v>-22.3559</v>
       </c>
       <c r="F25" t="n">
-        <v>1.909599999999999</v>
+        <v>1.909399999999999</v>
       </c>
       <c r="G25" t="n">
         <v>-17.7175</v>
       </c>
       <c r="H25" t="n">
-        <v>6.7222</v>
+        <v>6.722200000000001</v>
       </c>
       <c r="I25" t="n">
         <v>-24.4397</v>
@@ -2392,7 +2392,7 @@
         <v>-0.6862999999999999</v>
       </c>
       <c r="O25" t="n">
-        <v>-6.235500000000001</v>
+        <v>-6.2355</v>
       </c>
       <c r="P25" t="n">
         <v>-4.350099999999999</v>
@@ -2404,13 +2404,13 @@
         <v>10.8751</v>
       </c>
       <c r="S25" t="n">
-        <v>3.6652</v>
+        <v>3.6654</v>
       </c>
       <c r="T25" t="n">
         <v>1.9289</v>
       </c>
       <c r="U25" t="n">
-        <v>1.7364</v>
+        <v>1.7363</v>
       </c>
       <c r="V25" t="n">
         <v>-2.044</v>
